--- a/sheets/조재수대금교본/검수/stand by your man.xlsx
+++ b/sheets/조재수대금교본/검수/stand by your man.xlsx
@@ -6406,17 +6406,9 @@
         </is>
       </c>
       <c r="I5" s="23"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="23"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="23"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
@@ -6430,26 +6422,14 @@
         </is>
       </c>
       <c r="Q5" s="23"/>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R5" s="21"/>
       <c r="S5" s="23"/>
-      <c r="T5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
     <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
@@ -6503,8 +6483,7 @@
       <c r="S6" s="24"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U6" s="24"/>
@@ -6581,7 +6560,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="C8" s="23"/>
@@ -6614,11 +6593,7 @@
       <c r="C9" s="23"/>
       <c r="D9" s="21"/>
       <c r="E9" s="23"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="23"/>
       <c r="H9" s="21"/>
       <c r="I9" s="23"/>
@@ -6636,11 +6611,7 @@
         </is>
       </c>
       <c r="M9" s="23"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N9" s="21"/>
       <c r="O9" s="23"/>
       <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
@@ -6688,7 +6659,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="M10" s="24"/>
@@ -6711,18 +6682,14 @@
       <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="U10" s="24"/>
     </row>
     <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
@@ -6973,7 +6940,7 @@
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="E16" s="23"/>
@@ -7259,11 +7226,7 @@
       <c r="O24" s="24"/>
       <c r="P24" s="21"/>
       <c r="Q24" s="24"/>
-      <c r="R24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R24" s="21"/>
       <c r="S24" s="24"/>
       <c r="T24" s="21" t="inlineStr">
         <is>
@@ -7397,15 +7360,13 @@
       <c r="J28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M28" s="24"/>
@@ -7414,8 +7375,7 @@
       <c r="P28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="Q28" s="24"/>
@@ -7448,7 +7408,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M29" s="22"/>
@@ -7552,8 +7512,7 @@
       <c r="M32" s="24"/>
       <c r="N32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O32" s="24"/>

--- a/sheets/조재수대금교본/검수/stand by your man.xlsx
+++ b/sheets/조재수대금교본/검수/stand by your man.xlsx
@@ -6406,9 +6406,17 @@
         </is>
       </c>
       <c r="I5" s="23"/>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K5" s="23"/>
-      <c r="L5" s="21"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M5" s="23"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
@@ -6422,9 +6430,17 @@
         </is>
       </c>
       <c r="Q5" s="23"/>
-      <c r="R5" s="21"/>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S5" s="23"/>
-      <c r="T5" s="21"/>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U5" s="23"/>
     </row>
     <row r="6" ht="91.25" customHeight="true">
@@ -6483,7 +6499,8 @@
       <c r="S6" s="24"/>
       <c r="T6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="U6" s="24"/>
@@ -6560,7 +6577,7 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="C8" s="23"/>
@@ -6659,7 +6676,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="M10" s="24"/>
@@ -6682,7 +6699,7 @@
       <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="U10" s="24"/>
@@ -6940,7 +6957,7 @@
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="E16" s="23"/>
@@ -7408,7 +7425,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="M29" s="22"/>

--- a/sheets/조재수대금교본/검수/stand by your man.xlsx
+++ b/sheets/조재수대금교본/검수/stand by your man.xlsx
@@ -6199,32 +6199,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
     <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="81.63" customHeight="true">
+    <row r="20" ht="80.0" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="91.25" customHeight="true">
+    <row r="21" ht="89.42" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="91.25" customHeight="true">
+    <row r="22" ht="89.42" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="91.25" customHeight="true">
+    <row r="23" ht="89.42" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="23"/>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="U23" s="23"/>
     </row>
-    <row r="24" ht="91.25" customHeight="true">
+    <row r="24" ht="89.42" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="24"/>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="91.25" customHeight="true">
+    <row r="25" ht="89.42" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="91.25" customHeight="true">
+    <row r="26" ht="89.42" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -7332,7 +7332,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="91.25" customHeight="true">
+    <row r="27" ht="89.42" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7364,7 +7364,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="91.25" customHeight="true">
+    <row r="28" ht="89.42" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -7406,7 +7406,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="24"/>
     </row>
-    <row r="29" ht="91.25" customHeight="true">
+    <row r="29" ht="89.42" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="91.25" customHeight="true">
+    <row r="30" ht="89.42" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="U30" s="23"/>
     </row>
-    <row r="31" ht="91.25" customHeight="true">
+    <row r="31" ht="89.42" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="91.25" customHeight="true">
+    <row r="32" ht="89.42" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="U32" s="24"/>
     </row>
-    <row r="33" ht="91.25" customHeight="true">
+    <row r="33" ht="89.42" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="91.25" customHeight="true">
+    <row r="34" ht="89.42" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="91.25" customHeight="true">
+    <row r="35" ht="89.42" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="91.25" customHeight="true">
+    <row r="36" ht="89.42" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -7691,7 +7691,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
